--- a/QB Data Project/analysis/qb_data_analysis.xlsx
+++ b/QB Data Project/analysis/qb_data_analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr hidePivotFieldList="1"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Important Documents\Portfolio Project\QB_Stats_Dashboard\QB Data Project\analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mikegreen15/Documents/Portfolio/QB Data Project/analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{625515AD-E8C9-459A-83FA-94E6000702C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC9827B-FD3F-E04F-A2DC-FB3D02B1DA82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="500" windowWidth="33600" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Analysis" sheetId="13" r:id="rId1"/>
@@ -27,18 +27,17 @@
   <definedNames>
     <definedName name="Slicer_Player">#N/A</definedName>
     <definedName name="Slicer_Total_Games_Played_2015_2024">#N/A</definedName>
-    <definedName name="Slicer_Total_Interceptions_2015_2024">#N/A</definedName>
     <definedName name="Slicer_Total_passing_TDs_2015_2024">#N/A</definedName>
     <definedName name="Slicer_Total_Passing_Yards_2015_2024">#N/A</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId11"/>
-    <pivotCache cacheId="1" r:id="rId12"/>
-    <pivotCache cacheId="2" r:id="rId13"/>
-    <pivotCache cacheId="3" r:id="rId14"/>
-    <pivotCache cacheId="4" r:id="rId15"/>
-    <pivotCache cacheId="5" r:id="rId16"/>
+    <pivotCache cacheId="58" r:id="rId11"/>
+    <pivotCache cacheId="59" r:id="rId12"/>
+    <pivotCache cacheId="60" r:id="rId13"/>
+    <pivotCache cacheId="61" r:id="rId14"/>
+    <pivotCache cacheId="72" r:id="rId15"/>
+    <pivotCache cacheId="77" r:id="rId16"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -47,7 +46,6 @@
         <x14:slicerCache r:id="rId18"/>
         <x14:slicerCache r:id="rId19"/>
         <x14:slicerCache r:id="rId20"/>
-        <x14:slicerCache r:id="rId21"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -58,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="107">
   <si>
     <t>Player</t>
   </si>
@@ -385,7 +383,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -461,7 +459,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -473,27 +471,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <font>
         <b/>
@@ -521,6 +506,20 @@
         </right>
         <top/>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
       </border>
     </dxf>
     <dxf>
@@ -738,11 +737,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -781,9 +775,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -791,34 +788,18 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="1">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
+              <a:rPr lang="en-US" b="1"/>
               <a:t>Total Passing</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="1" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
+              <a:rPr lang="en-US" b="1" baseline="0"/>
               <a:t> Yards (2015-2025</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
+              <a:rPr lang="en-US" baseline="0"/>
               <a:t>)</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" sz="1600">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:endParaRPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -835,9 +816,12 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -2728,7 +2712,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx2">
                       <a:lumMod val="50000"/>
@@ -2756,17 +2740,7 @@
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.18404269770226581"/>
-          <c:y val="0.12235960740185808"/>
-          <c:w val="0.76961195851245201"/>
-          <c:h val="0.78210291487212635"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
@@ -2810,7 +2784,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx2">
                         <a:lumMod val="50000"/>
@@ -3006,7 +2980,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:ln w="6350">
                   <a:noFill/>
                 </a:ln>
@@ -3080,9 +3054,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -3090,11 +3067,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1050" b="1">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
+                  <a:rPr lang="en-US" b="1"/>
                   <a:t>Passing Yards</a:t>
                 </a:r>
               </a:p>
@@ -3113,9 +3086,12 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -3142,12 +3118,15 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:ln>
                   <a:noFill/>
                 </a:ln>
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -3270,6 +3249,7 @@
       <c14:pivotOptions>
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
@@ -3307,9 +3287,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -3317,11 +3300,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="1">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
+              <a:rPr lang="en-US" b="1"/>
               <a:t>Average Yards Thrown Downfield</a:t>
             </a:r>
           </a:p>
@@ -3340,9 +3319,12 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -3710,9 +3692,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -3720,11 +3705,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1050" b="1">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
+                  <a:rPr lang="en-US" b="1"/>
                   <a:t>Season </a:t>
                 </a:r>
               </a:p>
@@ -3743,9 +3724,12 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -3778,9 +3762,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -3825,9 +3812,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -3835,11 +3825,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1050" b="1">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
+                  <a:rPr lang="en-US" b="1"/>
                   <a:t>Yards</a:t>
                 </a:r>
               </a:p>
@@ -3858,9 +3844,12 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -3887,9 +3876,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -4012,6 +4004,7 @@
       <c14:pivotOptions>
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
@@ -4051,7 +4044,10 @@
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -4059,26 +4055,14 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1400" b="1">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
+              <a:rPr lang="en-US" b="1"/>
               <a:t>Average Total</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
+              <a:rPr lang="en-US" b="1" baseline="0"/>
               <a:t> Pass Yards Per Season</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" sz="1400" b="1">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:endParaRPr>
+            <a:endParaRPr lang="en-US" b="1"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -4097,7 +4081,10 @@
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -4485,9 +4472,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -4495,11 +4485,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1050" b="1">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
+                  <a:rPr lang="en-US" b="1"/>
                   <a:t>Season</a:t>
                 </a:r>
               </a:p>
@@ -4518,9 +4504,12 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -4553,9 +4542,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -4601,9 +4593,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -4611,11 +4606,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1050" b="1">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
+                  <a:rPr lang="en-US" b="1"/>
                   <a:t>Yards</a:t>
                 </a:r>
               </a:p>
@@ -4642,9 +4633,12 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -4671,9 +4665,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -4763,6 +4760,7 @@
       <c14:pivotOptions>
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
@@ -4884,9 +4882,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>top_30_passer_rating!$A$2:$A$16</c:f>
+              <c:f>top_30_passer_rating!$A$2:$A$15</c:f>
               <c:strCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>Aaron Rodgers</c:v>
                 </c:pt>
@@ -4929,18 +4927,15 @@
                 <c:pt idx="13">
                   <c:v>Russell Wilson</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>Joe Burrow</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>top_30_passer_rating!$B$2:$B$16</c:f>
+              <c:f>top_30_passer_rating!$B$2:$B$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>122.68</c:v>
                 </c:pt>
@@ -4982,9 +4977,6 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>111.94</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>111.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5187,9 +5179,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -5197,26 +5192,14 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="1">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
+              <a:rPr lang="en-US" b="1"/>
               <a:t>Playoff</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="1" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
+              <a:rPr lang="en-US" b="1" baseline="0"/>
               <a:t> Passing Yard Leaders (2015-2024)</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" sz="1600" b="1">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:endParaRPr>
+            <a:endParaRPr lang="en-US" b="1"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -5233,9 +5216,12 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -5418,17 +5404,7 @@
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.19797354772341053"/>
-          <c:y val="0.15118171978120773"/>
-          <c:w val="0.76168559377745049"/>
-          <c:h val="0.78714810007374436"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
@@ -5611,9 +5587,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -5667,9 +5646,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -5758,6 +5740,7 @@
       <c14:pivotOptions>
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
@@ -5797,7 +5780,10 @@
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -5805,26 +5791,14 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1400" b="1">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
+              <a:rPr lang="en-US" b="1"/>
               <a:t>Average QB</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
+              <a:rPr lang="en-US" b="1" baseline="0"/>
               <a:t> Rushing Yards Per Season</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" sz="1400" b="1">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:endParaRPr>
+            <a:endParaRPr lang="en-US" b="1"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -5843,7 +5817,10 @@
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -6191,9 +6168,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -6201,11 +6181,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1050" b="1">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
+                  <a:rPr lang="en-US"/>
                   <a:t>Season</a:t>
                 </a:r>
               </a:p>
@@ -6224,9 +6200,12 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -6259,9 +6238,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -6307,9 +6289,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -6317,11 +6302,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1050">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
+                  <a:rPr lang="en-US"/>
                   <a:t>Avg Yards</a:t>
                 </a:r>
               </a:p>
@@ -6340,9 +6321,12 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -6369,9 +6353,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -6461,6 +6448,7 @@
       <c14:pivotOptions>
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
@@ -9744,9 +9732,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>978202</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>1073452</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>120951</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9775,16 +9763,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>2267</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>45357</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>126395</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>54428</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>154063</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>235857</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>169333</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9813,16 +9801,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>61956</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>243384</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>155032</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>113772</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>151529</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>930509</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9851,16 +9839,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>86200</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>167065</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>925307</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>151190</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>138016</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>187292</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>117528</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>171417</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9889,16 +9877,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>175683</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>57534</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>16933</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>15874</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>787191</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>135467</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9928,18 +9916,18 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>968979</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>43846</xdr:rowOff>
+      <xdr:colOff>1080105</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>75596</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>1095375</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>79375</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>362857</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>145893</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="16" name="Player">
@@ -9962,7 +9950,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -9972,8 +9960,164 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6302979" y="6411989"/>
-              <a:ext cx="2521253" cy="3083529"/>
+              <a:off x="6819219" y="3628381"/>
+              <a:ext cx="2658701" cy="2385234"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1058332</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>59267</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>816429</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>129564</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="17" name="Total Passing Yards 2015-2024">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64E4CDAF-A9FC-5279-A19F-91C8761B404A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Total Passing Yards 2015-2024"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="11282636" y="3612052"/>
+              <a:ext cx="1960502" cy="2385234"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>382208</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>58058</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1043216</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>128355</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="18" name="Total passing TDs 2015-2024">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACE7E8F3-F020-3532-EDC6-83A366E33A00}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Total passing TDs 2015-2024"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9497271" y="3610843"/>
+              <a:ext cx="1770249" cy="2385234"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -10006,174 +10150,18 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>296331</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>59266</xdr:rowOff>
+      <xdr:colOff>1814</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>40520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>13756</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>92794</xdr:rowOff>
+      <xdr:colOff>45357</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>110817</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="17" name="Total Passing Yards 2015-2024">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64E4CDAF-A9FC-5279-A19F-91C8761B404A}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Total Passing Yards 2015-2024"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="14406938" y="6427409"/>
-              <a:ext cx="1826532" cy="3081528"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100"/>
-                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
-If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>128208</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>42183</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>544133</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>79375</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="18" name="Total passing TDs 2015-2024">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACE7E8F3-F020-3532-EDC6-83A366E33A00}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Total passing TDs 2015-2024"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="10687351" y="6410326"/>
-              <a:ext cx="1831068" cy="3085192"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100"/>
-                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
-If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>1081314</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>84364</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>79375</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="20" name="Total Games Played 2015-2024">
@@ -10196,7 +10184,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -10206,8 +10194,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="8810171" y="6415768"/>
-              <a:ext cx="1833336" cy="3079750"/>
+              <a:off x="13248396" y="3593305"/>
+              <a:ext cx="1763670" cy="2385234"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -10240,15 +10228,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>15269</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>177346</xdr:rowOff>
+      <xdr:colOff>135466</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>67085</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>164646</xdr:rowOff>
+      <xdr:colOff>812800</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10273,84 +10261,6 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>593725</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>53974</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>279400</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>87502</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="6" name="Total Interceptions 2015-2024">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADDEADB4-FB30-CCFF-199B-0D08EBAB8445}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Total Interceptions 2015-2024"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="12568011" y="6422117"/>
-              <a:ext cx="1821996" cy="3081528"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100"/>
-                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
-If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -11937,10 +11847,10 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8DB5CFD8-D837-1E46-AD2E-D1B07C4DB65D}" name="PivotTable13" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="I2:P32" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8DB5CFD8-D837-1E46-AD2E-D1B07C4DB65D}" name="PivotTable13" cacheId="72" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="I2:P17" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
+    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
       <items count="31">
         <item x="7"/>
         <item x="13"/>
@@ -12214,7 +12124,7 @@
   <rowFields count="1">
     <field x="0"/>
   </rowFields>
-  <rowItems count="30">
+  <rowItems count="15">
     <i>
       <x v="17"/>
     </i>
@@ -12231,13 +12141,7 @@
       <x v="29"/>
     </i>
     <i>
-      <x v="12"/>
-    </i>
-    <i>
       <x v="21"/>
-    </i>
-    <i>
-      <x/>
     </i>
     <i>
       <x v="23"/>
@@ -12249,37 +12153,13 @@
       <x v="24"/>
     </i>
     <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
       <x v="9"/>
-    </i>
-    <i>
-      <x v="11"/>
     </i>
     <i>
       <x v="27"/>
     </i>
     <i>
-      <x v="5"/>
-    </i>
-    <i>
       <x v="16"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="18"/>
     </i>
     <i>
       <x v="13"/>
@@ -12288,22 +12168,7 @@
       <x v="8"/>
     </i>
     <i>
-      <x v="4"/>
-    </i>
-    <i>
       <x v="19"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="26"/>
     </i>
   </rowItems>
   <colFields count="1">
@@ -12341,16 +12206,16 @@
     <dataField name="Passer Rating" fld="7" baseField="0" baseItem="0"/>
     <dataField name="Games Played" fld="4" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="1">
-    <format dxfId="18">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
   <pivotTableStyleInfo name="PivotStyleMedium15" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="1" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" evalOrder="-1" id="15" iMeasureFld="5">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="15" filterVal="15"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -12363,7 +12228,212 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{40134FB9-C0B6-DC45-90D5-879615FDB3E5}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B532CA54-6A53-7943-A3F4-1638E1DAE7AF}" name="PivotTable14" cacheId="77" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="G17:H27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="11">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="10">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Average QB Rushing" fld="0" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleMedium6" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A522A3B1-4A1B-E642-B1DB-11EC6783AA2E}" name="PivotTable10" cacheId="60" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="D3:E13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField dataField="1" showAll="0">
+      <items count="11">
+        <item x="8"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="11">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="10">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Average Passing Yards" fld="0" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="5" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{40134FB9-C0B6-DC45-90D5-879615FDB3E5}" name="PivotTable9" cacheId="59" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A17:B32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="ascending">
@@ -12540,8 +12610,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{573C6BAB-546E-9147-AFB3-1E6BB81C375D}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{573C6BAB-546E-9147-AFB3-1E6BB81C375D}" name="PivotTable6" cacheId="58" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="A3:B13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField dataField="1" showAll="0"/>
@@ -12625,8 +12695,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F6F1C2C9-8024-5044-8E3B-F16A56022893}" name="PivotTable12" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F6F1C2C9-8024-5044-8E3B-F16A56022893}" name="PivotTable12" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
   <location ref="D18:E33" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="ascending">
@@ -12812,211 +12882,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B532CA54-6A53-7943-A3F4-1638E1DAE7AF}" name="PivotTable14" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
-  <location ref="G17:H27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="11">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="10">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Average QB Rushing" fld="0" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="3">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="1" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleMedium6" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A522A3B1-4A1B-E642-B1DB-11EC6783AA2E}" name="PivotTable10" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
-  <location ref="D3:E13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
-    <pivotField dataField="1" showAll="0">
-      <items count="11">
-        <item x="8"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="11">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="10">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Average Passing Yards" fld="0" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="5" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Player" xr10:uid="{99D248D9-6CFF-E242-842F-DBFECEDB7012}" sourceName="Player">
   <pivotTables>
@@ -13185,53 +13050,12 @@
 </slicerCacheDefinition>
 </file>
 
-<file path=xl/slicerCaches/slicerCache5.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Total_Interceptions_2015_2024" xr10:uid="{71A570A8-8D95-4FFA-8DA4-4AE29F35972B}" sourceName="Total Interceptions 2015-2024">
-  <pivotTables>
-    <pivotTable tabId="13" name="PivotTable13"/>
-  </pivotTables>
-  <data>
-    <tabular pivotCacheId="1626502262">
-      <items count="26">
-        <i x="22" s="1"/>
-        <i x="16" s="1"/>
-        <i x="19" s="1"/>
-        <i x="20" s="1"/>
-        <i x="13" s="1"/>
-        <i x="7" s="1"/>
-        <i x="18" s="1"/>
-        <i x="23" s="1"/>
-        <i x="24" s="1"/>
-        <i x="15" s="1"/>
-        <i x="25" s="1"/>
-        <i x="21" s="1"/>
-        <i x="4" s="1"/>
-        <i x="17" s="1"/>
-        <i x="14" s="1"/>
-        <i x="8" s="1"/>
-        <i x="12" s="1"/>
-        <i x="9" s="1"/>
-        <i x="11" s="1"/>
-        <i x="3" s="1"/>
-        <i x="10" s="1"/>
-        <i x="6" s="1"/>
-        <i x="5" s="1"/>
-        <i x="1" s="1"/>
-        <i x="2" s="1"/>
-        <i x="0" s="1"/>
-      </items>
-    </tabular>
-  </data>
-</slicerCacheDefinition>
-</file>
-
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
   <slicer name="Player" xr10:uid="{E5E69E83-85E3-674D-AD1A-70550A2CE2EF}" cache="Slicer_Player" caption="Player" style="SlicerStyleOther1" rowHeight="230716"/>
   <slicer name="Total Passing Yards 2015-2024" xr10:uid="{492B5476-F6DB-B340-8960-93B1B9627CCA}" cache="Slicer_Total_Passing_Yards_2015_2024" caption="Total Passing Yards 2015-2024" startItem="8" style="SlicerStyleOther1" rowHeight="230716"/>
-  <slicer name="Total passing TDs 2015-2024" xr10:uid="{2A532A67-7961-2947-9B1B-35A0EBB13A2F}" cache="Slicer_Total_passing_TDs_2015_2024" caption="Passing TDs" style="SlicerStyleOther1" rowHeight="230716"/>
-  <slicer name="Total Games Played 2015-2024" xr10:uid="{E3C198BD-F2D5-2745-99F4-D95C4AAEC1D0}" cache="Slicer_Total_Games_Played_2015_2024" caption="Games Playes" startItem="8" style="SlicerStyleOther1" rowHeight="230716"/>
-  <slicer name="Total Interceptions 2015-2024" xr10:uid="{0EF40899-3A12-4DB2-AB7A-876FEEF1ABEA}" cache="Slicer_Total_Interceptions_2015_2024" caption="Total Interceptions 2015-2024" style="SlicerStyleOther1" rowHeight="241300"/>
+  <slicer name="Total passing TDs 2015-2024" xr10:uid="{2A532A67-7961-2947-9B1B-35A0EBB13A2F}" cache="Slicer_Total_passing_TDs_2015_2024" caption="Total passing TDs 2015-2024" style="SlicerStyleOther1" rowHeight="230716"/>
+  <slicer name="Total Games Played 2015-2024" xr10:uid="{E3C198BD-F2D5-2745-99F4-D95C4AAEC1D0}" cache="Slicer_Total_Games_Played_2015_2024" caption="Total Games Played 2015-2024" startItem="8" style="SlicerStyleOther1" rowHeight="230716"/>
 </slicers>
 </file>
 
@@ -13278,7 +13102,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{961CF644-10F6-064B-9469-589B7D08E247}" name="Table5" displayName="Table5" ref="A1:J31" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
   <autoFilter ref="A1:J31" xr:uid="{961CF644-10F6-064B-9469-589B7D08E247}">
     <filterColumn colId="1">
-      <top10 val="15" filterVal="111.2"/>
+      <top10 val="14" filterVal="111.94"/>
     </filterColumn>
   </autoFilter>
   <tableColumns count="10">
@@ -13315,7 +13139,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6280B04F-B80C-994D-9E47-D620955EAFD4}" name="Table1" displayName="Table1" ref="A1:E11" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6280B04F-B80C-994D-9E47-D620955EAFD4}" name="Table1" displayName="Table1" ref="A1:E11" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
   <autoFilter ref="A1:E11" xr:uid="{6280B04F-B80C-994D-9E47-D620955EAFD4}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{3F311932-DAB0-5648-84E1-1BAA72B08A74}" name="Average QB Rushing"/>
@@ -13613,27 +13437,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{244C5D2F-4FD6-7D4A-A0DA-8B77F5100D89}">
-  <dimension ref="I1:P32"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <dimension ref="I1:P17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="8" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="9:16" ht="36">
-      <c r="I1" s="5"/>
-      <c r="K1" s="6" t="s">
+    <row r="1" spans="9:16" ht="37" x14ac:dyDescent="0.45">
+      <c r="I1" s="6"/>
+      <c r="K1" s="7" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="9:16">
+    <row r="2" spans="9:16" x14ac:dyDescent="0.2">
       <c r="I2" s="2" t="s">
         <v>97</v>
       </c>
@@ -13659,784 +13483,394 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="9:16">
+    <row r="3" spans="9:16" x14ac:dyDescent="0.2">
       <c r="I3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="5">
         <v>39699</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="5">
         <v>267</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="5">
         <v>107</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="5">
         <v>69.08</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="5">
         <v>7.81</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="5">
         <v>101.1</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="5">
         <v>149</v>
       </c>
     </row>
-    <row r="4" spans="9:16">
+    <row r="4" spans="9:16" x14ac:dyDescent="0.2">
       <c r="I4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="5">
         <v>37975</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="5">
         <v>236</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="5">
         <v>100</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="5">
         <v>67.23</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="5">
         <v>7.48</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="5">
         <v>96.73</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="5">
         <v>153</v>
       </c>
     </row>
-    <row r="5" spans="9:16">
+    <row r="5" spans="9:16" x14ac:dyDescent="0.2">
       <c r="I5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="5">
         <v>37936</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="5">
         <v>244</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="5">
         <v>103</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="5">
         <v>67.06</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="5">
         <v>7.68</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="5">
         <v>97.55</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="5">
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="9:16">
+    <row r="6" spans="9:16" x14ac:dyDescent="0.2">
       <c r="I6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="5">
         <v>36185</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="5">
         <v>279</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="5">
         <v>85</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="5">
         <v>66.16</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="5">
         <v>7.76</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="5">
         <v>101.95</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="5">
         <v>151</v>
       </c>
     </row>
-    <row r="7" spans="9:16">
+    <row r="7" spans="9:16" x14ac:dyDescent="0.2">
       <c r="I7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="5">
         <v>35550</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="5">
         <v>254</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="5">
         <v>70</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="5">
         <v>66.48</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="5">
         <v>7.51</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="5">
         <v>100.81</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="5">
         <v>125</v>
       </c>
     </row>
-    <row r="8" spans="9:16">
+    <row r="8" spans="9:16" x14ac:dyDescent="0.2">
       <c r="I8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J8">
-        <v>34735</v>
-      </c>
-      <c r="K8">
-        <v>221</v>
-      </c>
-      <c r="L8">
-        <v>93</v>
-      </c>
-      <c r="M8">
-        <v>66.25</v>
-      </c>
-      <c r="N8">
+        <v>14</v>
+      </c>
+      <c r="J8" s="5">
+        <v>34626</v>
+      </c>
+      <c r="K8" s="5">
+        <v>201</v>
+      </c>
+      <c r="L8" s="5">
+        <v>92</v>
+      </c>
+      <c r="M8" s="5">
+        <v>68.319999999999993</v>
+      </c>
+      <c r="N8" s="5">
+        <v>7.76</v>
+      </c>
+      <c r="O8" s="5">
+        <v>97.63</v>
+      </c>
+      <c r="P8" s="5">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="9:16" x14ac:dyDescent="0.2">
+      <c r="I9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="5">
+        <v>32352</v>
+      </c>
+      <c r="K9" s="5">
+        <v>245</v>
+      </c>
+      <c r="L9" s="5">
+        <v>75</v>
+      </c>
+      <c r="M9" s="5">
+        <v>67.41</v>
+      </c>
+      <c r="N9" s="5">
+        <v>7.96</v>
+      </c>
+      <c r="O9" s="5">
+        <v>100.91</v>
+      </c>
+      <c r="P9" s="5">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="9:16" x14ac:dyDescent="0.2">
+      <c r="I10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="5">
+        <v>31230</v>
+      </c>
+      <c r="K10" s="5">
+        <v>213</v>
+      </c>
+      <c r="L10" s="5">
+        <v>82</v>
+      </c>
+      <c r="M10" s="5">
+        <v>68.08</v>
+      </c>
+      <c r="N10" s="5">
+        <v>7.71</v>
+      </c>
+      <c r="O10" s="5">
+        <v>99.19</v>
+      </c>
+      <c r="P10" s="5">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="9:16" x14ac:dyDescent="0.2">
+      <c r="I11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="5">
+        <v>26785</v>
+      </c>
+      <c r="K11" s="5">
+        <v>169</v>
+      </c>
+      <c r="L11" s="5">
+        <v>87</v>
+      </c>
+      <c r="M11" s="5">
+        <v>66.91</v>
+      </c>
+      <c r="N11" s="5">
+        <v>7.98</v>
+      </c>
+      <c r="O11" s="5">
+        <v>97.15</v>
+      </c>
+      <c r="P11" s="5">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="9:16" x14ac:dyDescent="0.2">
+      <c r="I12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" s="5">
+        <v>24091</v>
+      </c>
+      <c r="K12" s="5">
+        <v>172</v>
+      </c>
+      <c r="L12" s="5">
+        <v>48</v>
+      </c>
+      <c r="M12" s="5">
+        <v>73.099999999999994</v>
+      </c>
+      <c r="N12" s="5">
+        <v>8</v>
+      </c>
+      <c r="O12" s="5">
+        <v>109.42</v>
+      </c>
+      <c r="P12" s="5">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="9:16" x14ac:dyDescent="0.2">
+      <c r="I13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" s="5">
+        <v>23629</v>
+      </c>
+      <c r="K13" s="5">
+        <v>154</v>
+      </c>
+      <c r="L13" s="5">
+        <v>73</v>
+      </c>
+      <c r="M13" s="5">
+        <v>67.430000000000007</v>
+      </c>
+      <c r="N13" s="5">
+        <v>7.88</v>
+      </c>
+      <c r="O13" s="5">
+        <v>97.66</v>
+      </c>
+      <c r="P13" s="5">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="9:16" x14ac:dyDescent="0.2">
+      <c r="I14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J14" s="5">
+        <v>21093</v>
+      </c>
+      <c r="K14" s="5">
+        <v>137</v>
+      </c>
+      <c r="L14" s="5">
+        <v>45</v>
+      </c>
+      <c r="M14" s="5">
+        <v>67.349999999999994</v>
+      </c>
+      <c r="N14" s="5">
+        <v>7.32</v>
+      </c>
+      <c r="O14" s="5">
+        <v>98.24</v>
+      </c>
+      <c r="P14" s="5">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="9:16" x14ac:dyDescent="0.2">
+      <c r="I15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" s="5">
+        <v>19001</v>
+      </c>
+      <c r="K15" s="5">
+        <v>140</v>
+      </c>
+      <c r="L15" s="5">
+        <v>46</v>
+      </c>
+      <c r="M15" s="5">
+        <v>69.540000000000006</v>
+      </c>
+      <c r="N15" s="5">
+        <v>7.49</v>
+      </c>
+      <c r="O15" s="5">
+        <v>101.48</v>
+      </c>
+      <c r="P15" s="5">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="9:16" x14ac:dyDescent="0.2">
+      <c r="I16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="5">
+        <v>17773</v>
+      </c>
+      <c r="K16" s="5">
+        <v>124</v>
+      </c>
+      <c r="L16" s="5">
+        <v>47</v>
+      </c>
+      <c r="M16" s="5">
+        <v>65.930000000000007</v>
+      </c>
+      <c r="N16" s="5">
         <v>7.55</v>
       </c>
-      <c r="O8">
-        <v>95.58</v>
-      </c>
-      <c r="P8">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="9" spans="9:16">
-      <c r="I9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9">
-        <v>34626</v>
-      </c>
-      <c r="K9">
-        <v>201</v>
-      </c>
-      <c r="L9">
-        <v>92</v>
-      </c>
-      <c r="M9">
-        <v>68.319999999999993</v>
-      </c>
-      <c r="N9">
-        <v>7.76</v>
-      </c>
-      <c r="O9">
-        <v>97.63</v>
-      </c>
-      <c r="P9">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="10" spans="9:16">
-      <c r="I10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10">
-        <v>33407</v>
-      </c>
-      <c r="K10">
-        <v>270</v>
-      </c>
-      <c r="L10">
-        <v>55</v>
-      </c>
-      <c r="M10">
-        <v>59.19</v>
-      </c>
-      <c r="N10">
-        <v>6.55</v>
-      </c>
-      <c r="O10">
-        <v>95.86</v>
-      </c>
-      <c r="P10">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="11" spans="9:16">
-      <c r="I11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11">
-        <v>32352</v>
-      </c>
-      <c r="K11">
-        <v>245</v>
-      </c>
-      <c r="L11">
-        <v>75</v>
-      </c>
-      <c r="M11">
-        <v>67.41</v>
-      </c>
-      <c r="N11">
-        <v>7.96</v>
-      </c>
-      <c r="O11">
-        <v>100.91</v>
-      </c>
-      <c r="P11">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="9:16">
-      <c r="I12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12">
-        <v>31230</v>
-      </c>
-      <c r="K12">
-        <v>213</v>
-      </c>
-      <c r="L12">
-        <v>82</v>
-      </c>
-      <c r="M12">
-        <v>68.08</v>
-      </c>
-      <c r="N12">
-        <v>7.71</v>
-      </c>
-      <c r="O12">
-        <v>99.19</v>
-      </c>
-      <c r="P12">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="13" spans="9:16">
-      <c r="I13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13">
-        <v>26785</v>
-      </c>
-      <c r="K13">
-        <v>169</v>
-      </c>
-      <c r="L13">
-        <v>87</v>
-      </c>
-      <c r="M13">
-        <v>66.91</v>
-      </c>
-      <c r="N13">
-        <v>7.98</v>
-      </c>
-      <c r="O13">
-        <v>97.15</v>
-      </c>
-      <c r="P13">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="9:16">
-      <c r="I14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J14">
-        <v>26404</v>
-      </c>
-      <c r="K14">
-        <v>196</v>
-      </c>
-      <c r="L14">
-        <v>84</v>
-      </c>
-      <c r="M14">
-        <v>63.98</v>
-      </c>
-      <c r="N14">
-        <v>7.4</v>
-      </c>
-      <c r="O14">
-        <v>93.95</v>
-      </c>
-      <c r="P14">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" spans="9:16">
-      <c r="I15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15">
-        <v>24766</v>
-      </c>
-      <c r="K15">
-        <v>164</v>
-      </c>
-      <c r="L15">
-        <v>80</v>
-      </c>
-      <c r="M15">
-        <v>65.83</v>
-      </c>
-      <c r="N15">
-        <v>7.19</v>
-      </c>
-      <c r="O15">
-        <v>91.38</v>
-      </c>
-      <c r="P15">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="16" spans="9:16">
-      <c r="I16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16">
-        <v>24742</v>
-      </c>
-      <c r="K16">
-        <v>154</v>
-      </c>
-      <c r="L16">
-        <v>84</v>
-      </c>
-      <c r="M16">
-        <v>64.7</v>
-      </c>
-      <c r="N16">
-        <v>7.08</v>
-      </c>
-      <c r="O16">
-        <v>90.28</v>
-      </c>
-      <c r="P16">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="17" spans="9:16">
+      <c r="O16" s="5">
+        <v>96.92</v>
+      </c>
+      <c r="P16" s="5">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="9:16" x14ac:dyDescent="0.2">
       <c r="I17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17">
-        <v>24436</v>
-      </c>
-      <c r="K17">
-        <v>169</v>
-      </c>
-      <c r="L17">
-        <v>87</v>
-      </c>
-      <c r="M17">
-        <v>64.650000000000006</v>
-      </c>
-      <c r="N17">
-        <v>7.38</v>
-      </c>
-      <c r="O17">
-        <v>91.66</v>
-      </c>
-      <c r="P17">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="9:16">
-      <c r="I18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J18">
-        <v>24091</v>
-      </c>
-      <c r="K18">
-        <v>172</v>
-      </c>
-      <c r="L18">
-        <v>48</v>
-      </c>
-      <c r="M18">
-        <v>73.099999999999994</v>
-      </c>
-      <c r="N18">
-        <v>8</v>
-      </c>
-      <c r="O18">
-        <v>109.42</v>
-      </c>
-      <c r="P18">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="19" spans="9:16">
-      <c r="I19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19">
-        <v>23816</v>
-      </c>
-      <c r="K19">
-        <v>153</v>
-      </c>
-      <c r="L19">
-        <v>107</v>
-      </c>
-      <c r="M19">
-        <v>62.87</v>
-      </c>
-      <c r="N19">
-        <v>7.57</v>
-      </c>
-      <c r="O19">
-        <v>87.1</v>
-      </c>
-      <c r="P19">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="9:16">
-      <c r="I20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J20">
-        <v>23629</v>
-      </c>
-      <c r="K20">
-        <v>154</v>
-      </c>
-      <c r="L20">
-        <v>73</v>
-      </c>
-      <c r="M20">
-        <v>67.430000000000007</v>
-      </c>
-      <c r="N20">
-        <v>7.88</v>
-      </c>
-      <c r="O20">
-        <v>97.66</v>
-      </c>
-      <c r="P20">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="21" spans="9:16">
-      <c r="I21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J21">
-        <v>22410</v>
-      </c>
-      <c r="K21">
-        <v>153</v>
-      </c>
-      <c r="L21">
+        <v>33</v>
+      </c>
+      <c r="J17" s="5">
+        <v>17721</v>
+      </c>
+      <c r="K17" s="5">
+        <v>147</v>
+      </c>
+      <c r="L17" s="5">
+        <v>41</v>
+      </c>
+      <c r="M17" s="5">
         <v>67</v>
       </c>
-      <c r="M21">
-        <v>64.98</v>
-      </c>
-      <c r="N21">
-        <v>6.84</v>
-      </c>
-      <c r="O21">
-        <v>91.27</v>
-      </c>
-      <c r="P21">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" spans="9:16">
-      <c r="I22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J22">
-        <v>21093</v>
-      </c>
-      <c r="K22">
-        <v>137</v>
-      </c>
-      <c r="L22">
-        <v>45</v>
-      </c>
-      <c r="M22">
-        <v>67.349999999999994</v>
-      </c>
-      <c r="N22">
-        <v>7.32</v>
-      </c>
-      <c r="O22">
-        <v>98.24</v>
-      </c>
-      <c r="P22">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" spans="9:16">
-      <c r="I23" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J23">
-        <v>19912</v>
-      </c>
-      <c r="K23">
-        <v>107</v>
-      </c>
-      <c r="L23">
-        <v>71</v>
-      </c>
-      <c r="M23">
-        <v>63.9</v>
-      </c>
-      <c r="N23">
-        <v>6.95</v>
-      </c>
-      <c r="O23">
-        <v>88.88</v>
-      </c>
-      <c r="P23">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="24" spans="9:16">
-      <c r="I24" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J24">
-        <v>19279</v>
-      </c>
-      <c r="K24">
-        <v>115</v>
-      </c>
-      <c r="L24">
-        <v>56</v>
-      </c>
-      <c r="M24">
-        <v>68.42</v>
-      </c>
-      <c r="N24">
-        <v>7.09</v>
-      </c>
-      <c r="O24">
-        <v>94.38</v>
-      </c>
-      <c r="P24">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="25" spans="9:16">
-      <c r="I25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J25">
-        <v>19001</v>
-      </c>
-      <c r="K25">
-        <v>140</v>
-      </c>
-      <c r="L25">
-        <v>46</v>
-      </c>
-      <c r="M25">
-        <v>69.540000000000006</v>
-      </c>
-      <c r="N25">
-        <v>7.49</v>
-      </c>
-      <c r="O25">
-        <v>101.48</v>
-      </c>
-      <c r="P25">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" spans="9:16">
-      <c r="I26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J26">
-        <v>17773</v>
-      </c>
-      <c r="K26">
-        <v>124</v>
-      </c>
-      <c r="L26">
-        <v>47</v>
-      </c>
-      <c r="M26">
-        <v>65.930000000000007</v>
-      </c>
-      <c r="N26">
-        <v>7.55</v>
-      </c>
-      <c r="O26">
-        <v>96.92</v>
-      </c>
-      <c r="P26">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27" spans="9:16">
-      <c r="I27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J27">
-        <v>17759</v>
-      </c>
-      <c r="K27">
-        <v>110</v>
-      </c>
-      <c r="L27">
-        <v>69</v>
-      </c>
-      <c r="M27">
-        <v>60.13</v>
-      </c>
-      <c r="N27">
-        <v>6.95</v>
-      </c>
-      <c r="O27">
-        <v>80.599999999999994</v>
-      </c>
-      <c r="P27">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28" spans="9:16">
-      <c r="I28" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J28">
-        <v>17721</v>
-      </c>
-      <c r="K28">
-        <v>147</v>
-      </c>
-      <c r="L28">
-        <v>41</v>
-      </c>
-      <c r="M28">
-        <v>67</v>
-      </c>
-      <c r="N28">
+      <c r="N17" s="5">
         <v>7.18</v>
       </c>
-      <c r="O28">
+      <c r="O17" s="5">
         <v>99.2</v>
       </c>
-      <c r="P28">
+      <c r="P17" s="5">
         <v>91</v>
-      </c>
-    </row>
-    <row r="29" spans="9:16">
-      <c r="I29" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J29">
-        <v>17268</v>
-      </c>
-      <c r="K29">
-        <v>107</v>
-      </c>
-      <c r="L29">
-        <v>59</v>
-      </c>
-      <c r="M29">
-        <v>64.650000000000006</v>
-      </c>
-      <c r="N29">
-        <v>7.09</v>
-      </c>
-      <c r="O29">
-        <v>89.16</v>
-      </c>
-      <c r="P29">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30" spans="9:16">
-      <c r="I30" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J30">
-        <v>16073</v>
-      </c>
-      <c r="K30">
-        <v>98</v>
-      </c>
-      <c r="L30">
-        <v>66</v>
-      </c>
-      <c r="M30">
-        <v>62.63</v>
-      </c>
-      <c r="N30">
-        <v>7.15</v>
-      </c>
-      <c r="O30">
-        <v>86.6</v>
-      </c>
-      <c r="P30">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="31" spans="9:16">
-      <c r="I31" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J31">
-        <v>15981</v>
-      </c>
-      <c r="K31">
-        <v>96</v>
-      </c>
-      <c r="L31">
-        <v>55</v>
-      </c>
-      <c r="M31">
-        <v>69.89</v>
-      </c>
-      <c r="N31">
-        <v>7.48</v>
-      </c>
-      <c r="O31">
-        <v>95</v>
-      </c>
-      <c r="P31">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="32" spans="9:16">
-      <c r="I32" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J32">
-        <v>15717</v>
-      </c>
-      <c r="K32">
-        <v>100</v>
-      </c>
-      <c r="L32">
-        <v>68</v>
-      </c>
-      <c r="M32">
-        <v>62.09</v>
-      </c>
-      <c r="N32">
-        <v>6.95</v>
-      </c>
-      <c r="O32">
-        <v>85.48</v>
-      </c>
-      <c r="P32">
-        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -14456,9 +13890,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14478,7 +13912,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -14498,7 +13932,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -14518,7 +13952,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -14538,7 +13972,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -14558,7 +13992,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -14578,7 +14012,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -14598,7 +14032,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -14618,7 +14052,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -14638,7 +14072,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -14658,7 +14092,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -14678,7 +14112,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -14698,7 +14132,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -14718,7 +14152,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -14738,7 +14172,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -14758,7 +14192,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -14778,7 +14212,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>82</v>
       </c>
@@ -14798,7 +14232,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -14818,7 +14252,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -14838,7 +14272,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -14858,7 +14292,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -14878,7 +14312,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -14898,7 +14332,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -14918,7 +14352,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -14938,7 +14372,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>31</v>
       </c>
@@ -14958,7 +14392,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -14978,7 +14412,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -14998,7 +14432,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>83</v>
       </c>
@@ -15018,7 +14452,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>75</v>
       </c>
@@ -15038,7 +14472,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>8</v>
       </c>
@@ -15058,7 +14492,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>8</v>
       </c>
@@ -15086,39 +14520,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E132D88-3C58-F943-8F97-E000F2ACCC84}">
   <dimension ref="A3:H33"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="10" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="29" max="34" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="34" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>97</v>
       </c>
@@ -15132,7 +14566,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2015</v>
       </c>
@@ -15146,7 +14580,7 @@
         <v>3415.73</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>2016</v>
       </c>
@@ -15160,7 +14594,7 @@
         <v>3760.7</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>2017</v>
       </c>
@@ -15174,7 +14608,7 @@
         <v>3380.24</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>2018</v>
       </c>
@@ -15188,7 +14622,7 @@
         <v>3190.92</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>2019</v>
       </c>
@@ -15202,7 +14636,7 @@
         <v>3250.74</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>2020</v>
       </c>
@@ -15216,7 +14650,7 @@
         <v>3094.95</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>2021</v>
       </c>
@@ -15230,7 +14664,7 @@
         <v>3351.09</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>2022</v>
       </c>
@@ -15244,7 +14678,7 @@
         <v>2919.78</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>2023</v>
       </c>
@@ -15258,7 +14692,7 @@
         <v>2847.51</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>2024</v>
       </c>
@@ -15272,7 +14706,7 @@
         <v>2873.64</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>97</v>
       </c>
@@ -15286,7 +14720,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>22</v>
       </c>
@@ -15302,11 +14736,11 @@
       <c r="G18" s="3">
         <v>2015</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="5">
         <v>123.88</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>21</v>
       </c>
@@ -15322,11 +14756,11 @@
       <c r="G19" s="3">
         <v>2016</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="5">
         <v>125.72</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
@@ -15342,11 +14776,11 @@
       <c r="G20" s="3">
         <v>2017</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="5">
         <v>139.04</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>19</v>
       </c>
@@ -15362,11 +14796,11 @@
       <c r="G21" s="3">
         <v>2018</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="5">
         <v>151.72999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>18</v>
       </c>
@@ -15382,11 +14816,11 @@
       <c r="G22" s="3">
         <v>2019</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="5">
         <v>157.96</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>17</v>
       </c>
@@ -15402,11 +14836,11 @@
       <c r="G23" s="3">
         <v>2020</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="5">
         <v>148.31</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>16</v>
       </c>
@@ -15422,11 +14856,11 @@
       <c r="G24" s="3">
         <v>2021</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="5">
         <v>152.37</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>15</v>
       </c>
@@ -15442,11 +14876,11 @@
       <c r="G25" s="3">
         <v>2022</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="5">
         <v>160.22</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>14</v>
       </c>
@@ -15462,11 +14896,11 @@
       <c r="G26" s="3">
         <v>2023</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="5">
         <v>140.88</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>13</v>
       </c>
@@ -15482,11 +14916,11 @@
       <c r="G27" s="3">
         <v>2024</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="5">
         <v>178.25</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>12</v>
       </c>
@@ -15500,7 +14934,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>11</v>
       </c>
@@ -15514,7 +14948,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>10</v>
       </c>
@@ -15528,7 +14962,7 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>9</v>
       </c>
@@ -15542,7 +14976,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>8</v>
       </c>
@@ -15556,7 +14990,7 @@
         <v>4843</v>
       </c>
     </row>
-    <row r="33" spans="4:5">
+    <row r="33" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D33" s="3" t="s">
         <v>16</v>
       </c>
@@ -15572,19 +15006,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.1640625" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -15610,7 +15044,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -15636,7 +15070,7 @@
         <v>101.1</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -15662,7 +15096,7 @@
         <v>96.73</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -15688,7 +15122,7 @@
         <v>97.55</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -15714,7 +15148,7 @@
         <v>101.95</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -15740,7 +15174,7 @@
         <v>100.81</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -15766,7 +15200,7 @@
         <v>95.58</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -15792,7 +15226,7 @@
         <v>97.63</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -15818,7 +15252,7 @@
         <v>95.86</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -15844,7 +15278,7 @@
         <v>100.91</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -15870,7 +15304,7 @@
         <v>99.19</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -15896,7 +15330,7 @@
         <v>97.15</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -15922,7 +15356,7 @@
         <v>93.95</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -15948,7 +15382,7 @@
         <v>91.38</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -15974,7 +15408,7 @@
         <v>90.28</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -16000,7 +15434,7 @@
         <v>91.66</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -16026,7 +15460,7 @@
         <v>109.42</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -16052,7 +15486,7 @@
         <v>87.1</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -16078,7 +15512,7 @@
         <v>97.66</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -16104,7 +15538,7 @@
         <v>91.27</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -16130,7 +15564,7 @@
         <v>98.24</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -16156,7 +15590,7 @@
         <v>88.88</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>29</v>
       </c>
@@ -16182,7 +15616,7 @@
         <v>94.38</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>30</v>
       </c>
@@ -16208,7 +15642,7 @@
         <v>101.48</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>31</v>
       </c>
@@ -16234,7 +15668,7 @@
         <v>96.92</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>32</v>
       </c>
@@ -16260,7 +15694,7 @@
         <v>80.599999999999994</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -16286,7 +15720,7 @@
         <v>99.2</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>34</v>
       </c>
@@ -16312,7 +15746,7 @@
         <v>89.16</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>35</v>
       </c>
@@ -16338,7 +15772,7 @@
         <v>86.6</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>36</v>
       </c>
@@ -16364,7 +15798,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>37</v>
       </c>
@@ -16401,12 +15835,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>67</v>
       </c>
@@ -16414,7 +15848,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>7.62</v>
       </c>
@@ -16422,7 +15856,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>8.1</v>
       </c>
@@ -16430,7 +15864,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>7.81</v>
       </c>
@@ -16438,7 +15872,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>7.59</v>
       </c>
@@ -16446,7 +15880,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>8.01</v>
       </c>
@@ -16454,7 +15888,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>8.31</v>
       </c>
@@ -16462,7 +15896,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>8.4499999999999993</v>
       </c>
@@ -16470,7 +15904,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8.24</v>
       </c>
@@ -16478,7 +15912,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8.82</v>
       </c>
@@ -16486,7 +15920,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>8.5</v>
       </c>
@@ -16505,12 +15939,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>38</v>
       </c>
@@ -16518,7 +15952,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>3415.73</v>
       </c>
@@ -16526,7 +15960,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>3760.7</v>
       </c>
@@ -16534,7 +15968,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3380.24</v>
       </c>
@@ -16542,7 +15976,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3190.92</v>
       </c>
@@ -16550,7 +15984,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>3250.74</v>
       </c>
@@ -16558,7 +15992,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>3094.95</v>
       </c>
@@ -16566,7 +16000,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>3351.09</v>
       </c>
@@ -16574,7 +16008,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>2919.78</v>
       </c>
@@ -16582,7 +16016,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>2847.51</v>
       </c>
@@ -16590,7 +16024,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>2873.64</v>
       </c>
@@ -16609,19 +16043,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" customWidth="1"/>
-    <col min="2" max="3" width="13.42578125" customWidth="1"/>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="2" max="3" width="13.5" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="15.5" customWidth="1"/>
+    <col min="7" max="7" width="13.5" customWidth="1"/>
+    <col min="8" max="8" width="14.1640625" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -16653,7 +16087,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -16685,7 +16119,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -16717,7 +16151,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -16749,7 +16183,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -16781,7 +16215,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -16813,7 +16247,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -16845,7 +16279,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -16877,7 +16311,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>54</v>
       </c>
@@ -16909,7 +16343,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -16941,7 +16375,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -16973,7 +16407,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -17005,7 +16439,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -17037,7 +16471,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -17069,7 +16503,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -17101,7 +16535,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -17133,7 +16567,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -17165,7 +16599,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -17197,7 +16631,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -17229,7 +16663,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -17261,7 +16695,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -17293,7 +16727,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -17325,7 +16759,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -17357,7 +16791,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -17389,7 +16823,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -17421,7 +16855,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="26" spans="1:10" hidden="1">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -17453,7 +16887,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -17485,7 +16919,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -17517,7 +16951,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -17549,7 +16983,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>65</v>
       </c>
@@ -17581,7 +17015,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="31" spans="1:10" hidden="1">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -17624,19 +17058,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.140625" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" customWidth="1"/>
-    <col min="4" max="4" width="23.7109375" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" customWidth="1"/>
-    <col min="7" max="7" width="20.140625" customWidth="1"/>
+    <col min="1" max="1" width="23.1640625" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.1640625" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -17662,7 +17096,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -17688,7 +17122,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -17714,7 +17148,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -17740,7 +17174,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -17766,7 +17200,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -17792,7 +17226,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -17818,7 +17252,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -17844,7 +17278,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -17870,7 +17304,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -17896,7 +17330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>91</v>
       </c>
@@ -17922,7 +17356,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>54</v>
       </c>
@@ -17948,7 +17382,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -17974,7 +17408,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>75</v>
       </c>
@@ -18000,7 +17434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -18026,7 +17460,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>92</v>
       </c>
@@ -18052,7 +17486,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -18078,7 +17512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -18104,7 +17538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>93</v>
       </c>
@@ -18130,7 +17564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>94</v>
       </c>
@@ -18156,7 +17590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -18182,7 +17616,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>95</v>
       </c>
@@ -18208,7 +17642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -18234,7 +17668,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>96</v>
       </c>
@@ -18260,7 +17694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>83</v>
       </c>
@@ -18286,7 +17720,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -18323,15 +17757,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" customWidth="1"/>
+    <col min="3" max="3" width="23.83203125" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>76</v>
       </c>
@@ -18348,7 +17782,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>123.88</v>
       </c>
@@ -18365,7 +17799,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>125.72</v>
       </c>
@@ -18382,7 +17816,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>139.04</v>
       </c>
@@ -18399,7 +17833,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>151.72999999999999</v>
       </c>
@@ -18416,7 +17850,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>157.96</v>
       </c>
@@ -18433,7 +17867,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>148.31</v>
       </c>
@@ -18450,7 +17884,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>152.37</v>
       </c>
@@ -18467,7 +17901,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>160.22</v>
       </c>
@@ -18484,7 +17918,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>140.88</v>
       </c>
@@ -18501,7 +17935,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>178.25</v>
       </c>
@@ -18529,9 +17963,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -18557,7 +17991,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -18583,7 +18017,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -18609,7 +18043,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -18635,7 +18069,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -18661,7 +18095,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -18687,7 +18121,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -18713,7 +18147,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -18739,7 +18173,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -18765,7 +18199,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -18791,7 +18225,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -18817,7 +18251,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -18843,7 +18277,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -18869,7 +18303,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -18895,7 +18329,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -18921,7 +18355,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -18947,7 +18381,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -18973,7 +18407,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -18999,7 +18433,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -19025,7 +18459,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -19051,7 +18485,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -19077,7 +18511,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -19103,7 +18537,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>29</v>
       </c>
@@ -19129,7 +18563,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -19155,7 +18589,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -19181,7 +18615,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -19207,7 +18641,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -19233,7 +18667,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -19259,7 +18693,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -19285,7 +18719,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -19311,7 +18745,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>75</v>
       </c>
